--- a/tools/precos/planilhas/precos-oficiais-ROUND-LAB.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-ROUND-LAB.xlsx
@@ -570,12 +570,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MB003094</t>
+          <t>MB003109</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner: tônico 200 ml</t>
+          <t>1025 Dokdo Lotion: loção hidratante 400 ml</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>146.9</v>
+        <v>214.9</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -593,19 +593,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+          <t>1025 Dokdo Lotion</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" s="4" t="n">
-        <v>13.6</v>
+        <v>17.6</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -614,7 +610,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-toner?variant=43023567749334</t>
+          <t>https://roundlab.com/products/1025-dokdo-lotion</t>
         </is>
       </c>
       <c r="L2" s="2">
@@ -629,12 +625,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MB003117</t>
+          <t>MB000625</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner: tônico em tamanho grande 500 ml</t>
+          <t>1025 Dokdo Sleeping Pack: máscara noturna hidratante com PHA 100 ml</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -643,7 +639,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>247.9</v>
+        <v>174.9</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -652,19 +648,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>500ml</t>
-        </is>
-      </c>
+          <t>1025 Dokdo Sleeping Pack</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" s="4" t="n">
-        <v>27.2</v>
+        <v>19.2</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -673,7 +665,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-toner?variant=43023567782102</t>
+          <t>https://roundlab.com/products/1025-dokdo-sleeping-pack</t>
         </is>
       </c>
       <c r="L3" s="2">
@@ -688,12 +680,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MB003086</t>
+          <t>MB003094</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1025 Dokdo: sabonete líquido 200 ml</t>
+          <t>1025 Dokdo Toner: tônico 200 ml</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -702,7 +694,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>146.9</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -747,12 +739,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MB000581</t>
+          <t>MB003117</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Eye Cream: creme para a área dos olhos de camélia 30 ml</t>
+          <t>1025 Dokdo Toner: tônico em tamanho grande 500 ml</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -761,7 +753,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>217.9</v>
+        <v>247.9</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -770,14 +762,20 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Eye Cream 30ml</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>1025 Dokdo Toner</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="4" t="n"/>
+        <v>27.2</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -785,7 +783,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-eye-cream-30ml</t>
+          <t>https://roundlab.com/products/1025-dokdo-toner?variant=43023567782102</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -800,12 +798,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MB000575</t>
+          <t>MB003086</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Milky PDRN Toner: tônico leitoso de camélia e PDRN 150 ml</t>
+          <t>1025 Dokdo: sabonete líquido 200 ml</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -814,7 +812,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>210.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -823,14 +821,20 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Milky PDRN Toner 150ml</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1025 Dokdo Toner</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="I6" s="4" t="n"/>
+        <v>13.6</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -838,7 +842,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-milky-pdrn-toner-150ml</t>
+          <t>https://roundlab.com/products/1025-dokdo-toner?variant=43023567749334</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -853,21 +857,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MB003118</t>
+          <t>MB000581</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner 200ml</t>
+          <t>Camellia Deep Collagen Eye Cream: creme para a área dos olhos de camélia 30 ml</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>42.9</v>
+        <v>217.9</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -876,20 +880,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+          <t>Camellia Deep Collagen Eye Cream 30ml</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" s="4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>17</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="I7" s="4" t="n"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -897,7 +895,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-toner?variant=43023567749334</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-eye-cream-30ml</t>
         </is>
       </c>
       <c r="L7" s="2">
@@ -912,12 +910,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MB003124</t>
+          <t>MB000580</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleansing Milk: leite de limpeza hidratante 200 ml</t>
+          <t>Camellia Deep Collagen Firming Ampoule: ampola firmadora de camélia e colágeno 30 ml</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -926,25 +924,23 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>232.9</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleansing Gel</t>
+          <t>Camellia Deep Collagen Firming Ampoule</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" s="4" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>26</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -952,7 +948,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-cleansing-gel</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-firming-ampoule</t>
         </is>
       </c>
       <c r="L8" s="2">
@@ -967,12 +963,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MB003104</t>
+          <t>MB000575</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1025 Dokdo Eye Cream: creme hidratante para a área dos olhos 30 ml</t>
+          <t>Camellia Deep Collagen Milky PDRN Toner: tônico leitoso de camélia e PDRN 150 ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -981,25 +977,23 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>210.9</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cream</t>
+          <t>Camellia Deep Collagen Milky PDRN Toner 150ml</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" s="4" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>36</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I9" s="4" t="n"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1007,7 +1001,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-cream</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-milky-pdrn-toner-150ml</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -1022,12 +1016,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MB003109</t>
+          <t>MB000574</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1025 Dokdo Lotion: loção hidratante 400 ml</t>
+          <t>Camellia Deep Collagen V Lifting Gel Mask: máscara em gel para o contorno do queixo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1036,33 +1030,35 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>214.9</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>42.9</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1025 Dokdo Lotion</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Camellia Deep Collagen V Lifting Gel Mask</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>14PC</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>22</v>
-      </c>
+        <v>42.99</v>
+      </c>
+      <c r="I10" s="4" t="n"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-lotion</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-v-lifting-gel-mask?variant=47056525787350</t>
         </is>
       </c>
       <c r="L10" s="2">
@@ -1077,12 +1073,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MB000625</t>
+          <t>MB000559</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1025 Dokdo Sleeping Pack: máscara noturna hidratante com PHA 100 ml</t>
+          <t>Pine Calming Cica Body Wash: sabonete líquido corporal de pinheiro e cica 400 ml</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1093,23 +1089,21 @@
       <c r="D11" s="2" t="n">
         <v>174.9</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1025 Dokdo Sleeping Pack</t>
+          <t>Pine Calming Cica Body Wash</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" s="4" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="I11" s="4" t="n">
         <v>24</v>
       </c>
+      <c r="I11" s="4" t="n"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1117,7 +1111,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-sleeping-pack</t>
+          <t>https://roundlab.com/products/pine-cica-calming-body-wash</t>
         </is>
       </c>
       <c r="L11" s="2">
@@ -1132,12 +1126,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MB003096</t>
+          <t>MB000542</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner: kit com 2 tônicos (200 ml + 500 ml)</t>
+          <t>Soybean Nourishing Cleanser: espuma de limpeza esfoliante de soja 150 ml</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1146,21 +1140,21 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>371.9</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>108.9</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleanser + Dokdo Toner 200ml</t>
+          <t>Soybean Nourishing Cleanser</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" s="4" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I12" s="4" t="n"/>
       <c r="J12" t="inlineStr">
@@ -1170,7 +1164,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/dokdo-cleanser-dokdo-toner-the-perfect-gentle-routine</t>
+          <t>https://roundlab.com/products/soybean-nourishing-cleanser</t>
         </is>
       </c>
       <c r="L12" s="2">
@@ -1185,42 +1179,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MB000615</t>
+          <t>MB003118</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1025 Dokdo Water Gel Mask: máscara em folha de gel hidratante (brinde)</t>
+          <t>1025 Dokdo Toner 200ml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>42.9</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1025 Dokdo Water Gel Mask Sheet</t>
+          <t>1025 Dokdo Toner</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1 PC</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.2</v>
+        <v>13.6</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1229,7 +1223,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-mask-sheet?variant=44067260465366</t>
+          <t>https://roundlab.com/products/1025-dokdo-toner?variant=43023567749334</t>
         </is>
       </c>
       <c r="L13" s="2">
@@ -1244,12 +1238,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MB000619</t>
+          <t>MB003124</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1025 Dokdo Water Gel Mask: máscara em folha de gel hidratante 30 ml</t>
+          <t>1025 Dokdo Cleansing Milk: leite de limpeza hidratante 200 ml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1258,7 +1252,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>28.9</v>
+        <v>128.9</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -1267,19 +1261,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1025 Dokdo Water Gel Mask Sheet</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1 PC</t>
-        </is>
-      </c>
+          <t>1025 Dokdo Cleansing Gel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" s="4" t="n">
-        <v>3.2</v>
+        <v>20.8</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1288,7 +1278,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-mask-sheet?variant=44067260465366</t>
+          <t>https://roundlab.com/products/1025-dokdo-cleansing-gel</t>
         </is>
       </c>
       <c r="L14" s="2">
@@ -1303,12 +1293,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MB003969</t>
+          <t>MB003104</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1025 Dokdo: kit triplo de limpeza (150 ml × 3)</t>
+          <t>1025 Dokdo Eye Cream: creme hidratante para a área dos olhos 30 ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1317,7 +1307,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>371.9</v>
+        <v>104.9</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -1326,15 +1316,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner + Lotion Duo</t>
+          <t>1025 Dokdo Cream</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" s="4" t="n">
-        <v>31.2</v>
+        <v>28.8</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1343,7 +1333,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-toner-lotion-kit</t>
+          <t>https://roundlab.com/products/1025-dokdo-cream</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1358,12 +1348,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MB004048</t>
+          <t>MB003096</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Birch Juice Moisturizing Sunscreen: protetor solar hidratante 50 ml (kit com 3)</t>
+          <t>1025 Dokdo Toner: kit com 2 tônicos (200 ml + 500 ml)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1372,7 +1362,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>363.9</v>
+        <v>371.9</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -1381,16 +1371,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[DEAL] Birch Moisturizing Sunscreen Double Bundle</t>
+          <t>1025 Dokdo Cleanser + Dokdo Toner 200ml</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>56</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I16" s="4" t="n"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1398,7 +1386,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/double-pack-birch-moisturizing-sunscreen-uvlock-spf-45-broad-spectrum</t>
+          <t>https://roundlab.com/products/dokdo-cleanser-dokdo-toner-the-perfect-gentle-routine</t>
         </is>
       </c>
       <c r="L16" s="2">
@@ -1413,12 +1401,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MB000580</t>
+          <t>MB000615</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Firming Ampoule: ampola firmadora de camélia e colágeno 30 ml</t>
+          <t>1025 Dokdo Water Gel Mask: máscara em folha de gel hidratante (brinde)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1427,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>232.9</v>
+        <v>31.9</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -1436,14 +1424,20 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Firming Ampoule</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>1025 Dokdo Water Gel Mask Sheet</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1 PC</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="I17" s="4" t="n"/>
+        <v>3.2</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1451,7 +1445,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-firming-ampoule</t>
+          <t>https://roundlab.com/products/1025-dokdo-mask-sheet?variant=44067260465366</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1466,12 +1460,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MB000574</t>
+          <t>MB000619</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen V Lifting Gel Mask: máscara em gel para o contorno do queixo</t>
+          <t>1025 Dokdo Water Gel Mask: máscara em folha de gel hidratante 30 ml</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>42.9</v>
+        <v>28.9</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
@@ -1489,26 +1483,28 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen V Lifting Gel Mask</t>
+          <t>1025 Dokdo Water Gel Mask Sheet</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14PC</t>
+          <t>1 PC</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="I18" s="4" t="n"/>
+        <v>3.2</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-v-lifting-gel-mask?variant=47056525787350</t>
+          <t>https://roundlab.com/products/1025-dokdo-mask-sheet?variant=44067260465366</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1523,12 +1519,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MB003123</t>
+          <t>MB003969</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>For Men Birch Moisturizing Toner: tônico hidratante masculino de bétula 200 ml</t>
+          <t>1025 Dokdo: kit triplo de limpeza (150 ml × 3)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1537,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>128.9</v>
+        <v>371.9</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -1546,14 +1542,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birch Moisturizing Toner</t>
+          <t>1025 Dokdo Toner + Lotion Duo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="I19" s="4" t="n"/>
+        <v>31.2</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>39</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1561,7 +1559,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/birch-moisturizing-toner</t>
+          <t>https://roundlab.com/products/1025-dokdo-toner-lotion-kit</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1576,12 +1574,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB003037</t>
+          <t>MB004048</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>For Men Pine Calming Cica Cream: creme em gel calmante masculino de pinheiro 75 ml</t>
+          <t>Birch Juice Moisturizing Sunscreen: protetor solar hidratante 50 ml (kit com 3)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1590,7 +1588,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>144.9</v>
+        <v>363.9</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
@@ -1599,14 +1597,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Cream</t>
+          <t>[DEAL] Birch Moisturizing Sunscreen Double Bundle</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="I20" s="4" t="n"/>
+        <v>39</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>56</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-tree-cica-cream</t>
+          <t>https://roundlab.com/products/double-pack-birch-moisturizing-sunscreen-uvlock-spf-45-broad-spectrum</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1629,12 +1629,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB003036</t>
+          <t>MB003123</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>For Men Pine Calming Cica Lotion: loção calmante masculina de pinheiro 200 ml</t>
+          <t>For Men Birch Moisturizing Toner: tônico hidratante masculino de bétula 200 ml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>133.9</v>
+        <v>128.9</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Lotion</t>
+          <t>Birch Moisturizing Toner</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I21" s="4" t="n"/>
       <c r="J21" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-calming-cica-lotion</t>
+          <t>https://roundlab.com/products/birch-moisturizing-toner</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1682,12 +1682,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB003069</t>
+          <t>MB003037</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kit 1025 Dokdo: tônico 500 ml + loção hidratante 200 ml</t>
+          <t>For Men Pine Calming Cica Cream: creme em gel calmante masculino de pinheiro 75 ml</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>358.9</v>
+        <v>144.9</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
@@ -1705,16 +1705,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner + Lotion Duo</t>
+          <t>Pine Calming Cica Cream</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="4" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>39</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I22" s="4" t="n"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1722,7 +1720,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-toner-lotion-kit</t>
+          <t>https://roundlab.com/products/pine-tree-cica-cream</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1737,12 +1735,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB003129</t>
+          <t>MB003036</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Loção Dokdo 1025 200ml</t>
+          <t>For Men Pine Calming Cica Lotion: loção calmante masculina de pinheiro 200 ml</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1751,7 +1749,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>110.9</v>
+        <v>133.9</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -1760,20 +1758,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+          <t>Pine Calming Cica Lotion</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" s="4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>17</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I23" s="4" t="n"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1781,7 +1773,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-toner?variant=43023567749334</t>
+          <t>https://roundlab.com/products/pine-calming-cica-lotion</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1796,12 +1788,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB003059</t>
+          <t>MB003069</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Máscara de Gel Camellia Deep Collagen V-Lifting (4 unidades)</t>
+          <t>Kit 1025 Dokdo: tônico 500 ml + loção hidratante 200 ml</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1810,7 +1802,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>152.9</v>
+        <v>358.9</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -1819,19 +1811,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Camellia Collagen Slow Aging Routine</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Camellia Deep Collagen Firming Ampoule + Camellia Deep Collagen Firming Cream + 4 pc Camellia Deep Collagen Firming Gel Mask + Camellia Deep Collagen Jelly Mask Cleanser + 1 PC Camellia Deep Collagen V Lifting Gel Mask</t>
-        </is>
-      </c>
+          <t>1025 Dokdo Toner + Lotion Duo</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" s="4" t="n">
-        <v>87.73999999999999</v>
+        <v>31.2</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>116.99</v>
+        <v>39</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1840,7 +1828,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-collagen-slow-aging-routine</t>
+          <t>https://roundlab.com/products/1025-dokdo-toner-lotion-kit</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1855,12 +1843,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB003077</t>
+          <t>MB003059</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Body Mist: bruma corporal calmante de pinheiro 150 ml</t>
+          <t>Máscara de Gel Camellia Deep Collagen V-Lifting (4 unidades)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1869,7 +1857,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>123.9</v>
+        <v>152.9</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -1878,14 +1866,20 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Body Wash</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Camellia Collagen Slow Aging Routine</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Camellia Deep Collagen Firming Ampoule + Camellia Deep Collagen Firming Cream + 4 pc Camellia Deep Collagen Firming Gel Mask + Camellia Deep Collagen Jelly Mask Cleanser + 1 PC Camellia Deep Collagen V Lifting Gel Mask</t>
+        </is>
+      </c>
       <c r="H25" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I25" s="4" t="n"/>
+        <v>87.73999999999999</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>116.99</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1893,7 +1887,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-cica-calming-body-wash</t>
+          <t>https://roundlab.com/products/camellia-collagen-slow-aging-routine</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1908,12 +1902,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB000559</t>
+          <t>MB003077</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Body Wash: sabonete líquido corporal de pinheiro e cica 400 ml</t>
+          <t>Pine Calming Cica Body Mist: bruma corporal calmante de pinheiro 150 ml</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1922,7 +1916,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>174.9</v>
+        <v>123.9</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
@@ -1961,21 +1955,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB000542</t>
+          <t>MB003115</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Soybean Nourishing Cleanser: espuma de limpeza esfoliante de soja 150 ml</t>
+          <t>1025 Dokdo Cleanser 150ml</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>108.9</v>
+        <v>188.9</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
@@ -1984,14 +1978,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Soybean Nourishing Cleanser</t>
+          <t>1025 Dokdo Cleanser</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" s="4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="I27" s="4" t="n"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1999,7 +1995,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-nourishing-cleanser</t>
+          <t>https://roundlab.com/products/1025-dokdo-cleanser</t>
         </is>
       </c>
       <c r="L27" s="2">
@@ -2014,12 +2010,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB003115</t>
+          <t>MB003127</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleanser 150ml</t>
+          <t>Birch Moisturizing Sun Stick 19g</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2028,7 +2024,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>188.9</v>
+        <v>181.9</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
@@ -2037,16 +2033,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleanser</t>
+          <t>Birch Moisturizing Sun Stick SPF 50</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" s="4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>17</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I28" s="4" t="n"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2054,7 +2048,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-cleanser</t>
+          <t>https://roundlab.com/products/birch-moisturizing-sun-stick</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -2069,12 +2063,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB003127</t>
+          <t>MB003070</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Birch Moisturizing Sun Stick 19g</t>
+          <t>Calming Pine &amp; Cica Body Wash 400ml</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2083,7 +2077,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>181.9</v>
+        <v>175.9</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -2092,12 +2086,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birch Moisturizing Sun Stick SPF 50</t>
+          <t>Pine Calming Cica Body Wash</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I29" s="4" t="n"/>
       <c r="J29" t="inlineStr">
@@ -2107,7 +2101,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/birch-moisturizing-sun-stick</t>
+          <t>https://roundlab.com/products/pine-cica-calming-body-wash</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2122,12 +2116,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB003076</t>
+          <t>MB003065</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Birch: espuma de barbear masculina 120 ml</t>
+          <t>Round Lab Sonamu Cica Deep Pore Clay Pack Cleanser 150 ml</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2136,7 +2130,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>153.9</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -2145,12 +2139,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Birch Moisturizing Eye Balm</t>
+          <t>Pine Cica Deep Pore Clay Mask Cleanser</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I30" s="4" t="n"/>
       <c r="J30" t="inlineStr">
@@ -2160,7 +2154,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/round-lab-birch-juice-moisturizing-eye-balm-10g</t>
+          <t>https://roundlab.com/products/pine-cica-deep-pore-clay-mask-cleanser</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2175,37 +2169,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MB003070</t>
+          <t>MB003058</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Calming Pine &amp; Cica Body Wash 400ml</t>
+          <t>Camellia Deep Collagen Firming Sun Serum: sérum protetor solar firmador 50 ml</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>175.9</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>150.9</v>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Body Wash</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Anti-Aging Sheet Mask Bundle</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>10 PC Soybean Panthenol Sheet Mask + 10 PC Vita Niacinamide Dark Spot Serum Mask + 4 pc Camellia Deep Collagen Firming Gel Mask + 4PC Camellia Deep Collagen V Lifting Gel Mask</t>
+        </is>
+      </c>
       <c r="H31" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I31" s="4" t="n"/>
+        <v>99.22</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>132.29</v>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-cica-calming-body-wash</t>
+          <t>https://roundlab.com/products/anti-aging-sheet-mask-bundle</t>
         </is>
       </c>
       <c r="L31" s="2">
@@ -2228,12 +2228,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MB003093</t>
+          <t>MB003121</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Loção Dokdo 1025 200ml</t>
+          <t>1025 Dokdo Cleanser 150ml Conjunto com 2 unidades</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2242,29 +2242,23 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>110.9</v>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>195.9</v>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
+          <t>1025 Dokdo Cleanser + Dokdo Toner 200ml</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" s="4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>17</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I32" s="4" t="n"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2272,7 +2266,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-toner?variant=43023567749334</t>
+          <t>https://roundlab.com/products/dokdo-cleanser-dokdo-toner-the-perfect-gentle-routine</t>
         </is>
       </c>
       <c r="L32" s="2">
@@ -2287,12 +2281,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MB003065</t>
+          <t>MB003125</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Round Lab Sonamu Cica Deep Pore Clay Pack Cleanser 150 ml</t>
+          <t>Birch hydrating calming gel 150ml</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2301,23 +2295,29 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>153.9</v>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>101.9</v>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pine Cica Deep Pore Clay Mask Cleanser</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Award Winning Favorites Night Routine</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>200ml 1025 Dokdo Toner + 1025 Dokdo Cleanser + 1025 Dokdo Cleansing Oil + Birch Moisturizing Cream + Pine Calming Cica Ampoule + [Gift] 1025 Dokdo Water Gel Sheet Mask</t>
+        </is>
+      </c>
       <c r="H33" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I33" s="4" t="n"/>
+        <v>94.13</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>125.5</v>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-cica-deep-pore-clay-mask-cleanser</t>
+          <t>https://roundlab.com/products/award-winning-favorites-night-routine</t>
         </is>
       </c>
       <c r="L33" s="2">
@@ -2340,21 +2340,21 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MB003058</t>
+          <t>MB003102</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Firming Sun Serum: sérum protetor solar firmador 50 ml</t>
+          <t>Óleo de Limpeza Dokdo 1025 200ml</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>150.9</v>
+        <v>188.9</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -2363,19 +2363,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anti-Aging Sheet Mask Bundle</t>
+          <t>Award Winning Favorites Night Routine</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10 PC Soybean Panthenol Sheet Mask + 10 PC Vita Niacinamide Dark Spot Serum Mask + 4 pc Camellia Deep Collagen Firming Gel Mask + 4PC Camellia Deep Collagen V Lifting Gel Mask</t>
+          <t>200ml 1025 Dokdo Toner + 1025 Dokdo Cleanser + 1025 Dokdo Cleansing Oil + Birch Moisturizing Cream + Pine Calming Cica Ampoule + [Gift] 1025 Dokdo Water Gel Sheet Mask</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>99.22</v>
+        <v>94.13</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>132.29</v>
+        <v>125.5</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/anti-aging-sheet-mask-bundle</t>
+          <t>https://roundlab.com/products/award-winning-favorites-night-routine</t>
         </is>
       </c>
       <c r="L34" s="2">
@@ -2399,37 +2399,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MB003121</t>
+          <t>MB003075</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleanser 150ml Conjunto com 2 unidades</t>
+          <t>1025 Bálsamo de Limpeza Dokdo 50ml</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>195.9</v>
+        <v>174.9</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+          <t>Fraco — conferir</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleanser + Dokdo Toner 200ml</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>1025 Dokdo Cleansing Balm 50ml</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>50ml</t>
+        </is>
+      </c>
       <c r="H35" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="I35" s="4" t="n"/>
+        <v>22.4</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>28</v>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2437,7 +2443,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/dokdo-cleanser-dokdo-toner-the-perfect-gentle-routine</t>
+          <t>https://roundlab.com/products/1025-dokdo-cleansing-balm-50ml</t>
         </is>
       </c>
       <c r="L35" s="2">
@@ -2452,42 +2458,38 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MB003125</t>
+          <t>MB003105</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Birch hydrating calming gel 150ml</t>
+          <t>1025 Dokdo Mist: bruma hidratante 150 ml</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>101.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+          <t>Fraco — conferir</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Award Winning Favorites Night Routine</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>200ml 1025 Dokdo Toner + 1025 Dokdo Cleanser + 1025 Dokdo Cleansing Oil + Birch Moisturizing Cream + Pine Calming Cica Ampoule + [Gift] 1025 Dokdo Water Gel Sheet Mask</t>
-        </is>
-      </c>
+          <t>1025 Dokdo Sleeping Pack</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" s="4" t="n">
-        <v>94.13</v>
+        <v>19.2</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>125.5</v>
+        <v>24</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2496,7 +2498,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/award-winning-favorites-night-routine</t>
+          <t>https://roundlab.com/products/1025-dokdo-sleeping-pack</t>
         </is>
       </c>
       <c r="L36" s="2">
@@ -2511,12 +2513,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MB003075</t>
+          <t>MB003129</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1025 Bálsamo de Limpeza Dokdo 50ml</t>
+          <t>Loção Dokdo 1025 200ml</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2525,7 +2527,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>174.9</v>
+        <v>110.9</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
@@ -2534,19 +2536,15 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleansing Balm 50ml</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>50ml</t>
-        </is>
-      </c>
+          <t>1025 Dokdo Lotion</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>22.4</v>
+        <v>17.6</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2555,7 +2553,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-cleansing-balm-50ml</t>
+          <t>https://roundlab.com/products/1025-dokdo-lotion</t>
         </is>
       </c>
       <c r="L37" s="2">
@@ -2570,12 +2568,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MB003072</t>
+          <t>MB003114</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1025 Creme Hidratante Dokdo 50ml</t>
+          <t>Moisturizing sunscreen with birch scent, 50ml</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2584,7 +2582,7 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>261.9</v>
+        <v>142.9</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
@@ -2593,20 +2591,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleansing Balm 50ml</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>50ml</t>
-        </is>
-      </c>
+          <t>Birch Moisturizing Sunscreen UVLock SPF 50 Broad Spectrum</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" s="4" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>28</v>
-      </c>
+        <v>24.99</v>
+      </c>
+      <c r="I38" s="4" t="n"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2614,7 +2606,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-cleansing-balm-50ml</t>
+          <t>https://roundlab.com/products/birch-moisturizing-uv-sunscreen</t>
         </is>
       </c>
       <c r="L38" s="2">
@@ -2629,12 +2621,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MB003105</t>
+          <t>MB003038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1025 Dokdo Mist: bruma hidratante 150 ml</t>
+          <t>Pine &amp; Cica Soothing Intimate Wash: sabonete íntimo calmante 150 ml</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2652,16 +2644,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1025 Dokdo Sleeping Pack</t>
+          <t>Pine Calming Cica Body Wash</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" s="4" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="I39" s="4" t="n">
         <v>24</v>
       </c>
+      <c r="I39" s="4" t="n"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2669,7 +2659,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-sleeping-pack</t>
+          <t>https://roundlab.com/products/pine-cica-calming-body-wash</t>
         </is>
       </c>
       <c r="L39" s="2">
@@ -2684,12 +2674,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MB003114</t>
+          <t>MB003057</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Moisturizing sunscreen with birch scent, 50ml</t>
+          <t>Pine Cica Plus: creme calmante 60 ml</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2698,7 +2688,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>142.9</v>
+        <v>225.9</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
@@ -2707,12 +2697,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Birch Moisturizing Sunscreen UVLock SPF 50 Broad Spectrum</t>
+          <t>Pine Calming Cica Cream</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" s="4" t="n">
-        <v>24.99</v>
+        <v>31</v>
       </c>
       <c r="I40" s="4" t="n"/>
       <c r="J40" t="inlineStr">
@@ -2722,7 +2712,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/birch-moisturizing-uv-sunscreen</t>
+          <t>https://roundlab.com/products/pine-tree-cica-cream</t>
         </is>
       </c>
       <c r="L40" s="2">
@@ -2737,12 +2727,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MB003038</t>
+          <t>MB003087</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pine &amp; Cica Soothing Intimate Wash: sabonete íntimo calmante 150 ml</t>
+          <t>Pine and cica soothing lotion 250ml</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2751,7 +2741,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>203.9</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
@@ -2760,12 +2750,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Body Wash</t>
+          <t>Pine Calming Cica Lotion</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I41" s="4" t="n"/>
       <c r="J41" t="inlineStr">
@@ -2775,7 +2765,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-cica-calming-body-wash</t>
+          <t>https://roundlab.com/products/pine-calming-cica-lotion</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2790,21 +2780,21 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MB003057</t>
+          <t>MB003097</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pine Cica Plus: creme calmante 60 ml</t>
+          <t>1025 Dokdo Cleanser 150 ml – Kit com 2 unidades</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>225.9</v>
+        <v>195.9</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
@@ -2813,14 +2803,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Shampoo</t>
+          <t>[DEAL] Dokdo Cleanser Double 2-Pack</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I42" s="4" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2828,7 +2820,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-calming-cica-shampoo</t>
+          <t>https://roundlab.com/products/deal-dokdo-cleanser-double-2-pack</t>
         </is>
       </c>
       <c r="L42" s="2">
@@ -2843,21 +2835,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MB003087</t>
+          <t>MB003113</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pine and cica soothing lotion 250ml</t>
+          <t>1025 Dokdo Gel Esfoliante 120ml</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>203.9</v>
+        <v>188.9</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
@@ -2866,14 +2858,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Lotion</t>
+          <t>1025 Dokdo Cleansing Gel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="I43" s="4" t="n"/>
+        <v>20.8</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2881,7 +2875,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-calming-cica-lotion</t>
+          <t>https://roundlab.com/products/1025-dokdo-cleansing-gel</t>
         </is>
       </c>
       <c r="L43" s="2">
@@ -2896,12 +2890,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MB003097</t>
+          <t>MB003048</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleanser 150 ml – Kit com 2 unidades</t>
+          <t>Baby Mild Sun Stick: protetor solar em bastão FPS 50+ PA++++ 21 g</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2910,7 +2904,7 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>195.9</v>
+        <v>139.9</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
@@ -2919,16 +2913,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dokdo Cleanser Double Bundle</t>
+          <t>Birch Moisturizing Sun Stick SPF 50</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I44" s="4" t="n"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2936,7 +2928,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/dokdo-cleanser-double-1</t>
+          <t>https://roundlab.com/products/birch-moisturizing-sun-stick</t>
         </is>
       </c>
       <c r="L44" s="2">
@@ -2951,12 +2943,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MB003113</t>
+          <t>MB003110</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1025 Dokdo Gel Esfoliante 120ml</t>
+          <t>Birch Moisturizing Cleansing Pads (60 discos)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2965,7 +2957,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>188.9</v>
+        <v>174.9</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
@@ -2974,16 +2966,14 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleansing Gel</t>
+          <t>Birch Juice Moisturizing Peeling Cleansing Oil</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" s="4" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>26</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I45" s="4" t="n"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2991,7 +2981,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-cleansing-gel</t>
+          <t>https://roundlab.com/products/birch-juice-moisturizing-peeling-cleansing-oil</t>
         </is>
       </c>
       <c r="L45" s="2">
@@ -3006,12 +2996,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MB003048</t>
+          <t>MB003120</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Baby Mild Sun Stick: protetor solar em bastão FPS 50+ PA++++ 21 g</t>
+          <t>Conjunto de 2 Tônicos Dokdo 1025 (200ml + 500ml)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3020,7 +3010,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>139.9</v>
+        <v>371.9</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
@@ -3029,12 +3019,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Birch Moisturizing Sun Stick SPF 50</t>
+          <t>1025 Dokdo Cleanser + Dokdo Toner 200ml</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I46" s="4" t="n"/>
       <c r="J46" t="inlineStr">
@@ -3044,7 +3034,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/birch-moisturizing-sun-stick</t>
+          <t>https://roundlab.com/products/dokdo-cleanser-dokdo-toner-the-perfect-gentle-routine</t>
         </is>
       </c>
       <c r="L46" s="2">
@@ -3059,12 +3049,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MB003110</t>
+          <t>MB003119</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Birch Moisturizing Cleansing Pads (60 discos)</t>
+          <t>Creme Dokdo 1025 80ml</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3073,7 +3063,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>174.9</v>
+        <v>116.9</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
@@ -3082,14 +3072,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Birch Juice Moisturizing Peeling Cleansing Oil</t>
+          <t>1025 Dokdo Cream</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I47" s="4" t="n"/>
+        <v>28.8</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>36</v>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3097,7 +3089,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/birch-juice-moisturizing-peeling-cleansing-oil</t>
+          <t>https://roundlab.com/products/1025-dokdo-cream</t>
         </is>
       </c>
       <c r="L47" s="2">
@@ -3112,12 +3104,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MB003120</t>
+          <t>MB003095</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Conjunto de 2 Tônicos Dokdo 1025 (200ml + 500ml)</t>
+          <t>Creme Dokdo 1025 80ml</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3126,7 +3118,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>371.9</v>
+        <v>116.9</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -3135,14 +3127,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1025 Dokdo Cleanser + Dokdo Toner 200ml</t>
+          <t>1025 Dokdo Cream</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="I48" s="4" t="n"/>
+        <v>28.8</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>36</v>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3150,7 +3144,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/dokdo-cleanser-dokdo-toner-the-perfect-gentle-routine</t>
+          <t>https://roundlab.com/products/1025-dokdo-cream</t>
         </is>
       </c>
       <c r="L48" s="2">
@@ -3165,12 +3159,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MB003119</t>
+          <t>MB003093</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Creme Dokdo 1025 80ml</t>
+          <t>Loção Dokdo 1025 200ml</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3179,7 +3173,7 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>116.9</v>
+        <v>110.9</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
@@ -3188,15 +3182,15 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner Pad</t>
+          <t>1025 Dokdo Lotion</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="4" t="n">
-        <v>21.6</v>
+        <v>17.6</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3205,7 +3199,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-pad</t>
+          <t>https://roundlab.com/products/1025-dokdo-lotion</t>
         </is>
       </c>
       <c r="L49" s="2">
@@ -3220,12 +3214,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MB003095</t>
+          <t>MB003045</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Creme Dokdo 1025 80ml</t>
+          <t>ROUND LAB Baby Mild Sunscreen FPS 50+ PA++++: protetor solar mineral infantil 60 ml</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3234,7 +3228,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>116.9</v>
+        <v>139.9</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
@@ -3243,16 +3237,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1025 Dokdo Toner Pad</t>
+          <t>Birch Mild-Up Sunscreen UVLock SPF 50 Broad Spectrum</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" s="4" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>27</v>
-      </c>
+        <v>24.99</v>
+      </c>
+      <c r="I50" s="4" t="n"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3260,7 +3252,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/1025-dokdo-pad</t>
+          <t>https://roundlab.com/products/birch-juice-mild-up-uvlock-sunscreen</t>
         </is>
       </c>
       <c r="L50" s="2">
@@ -3275,124 +3267,70 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MB003045</t>
+          <t>MB003072</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ROUND LAB Baby Mild Sunscreen FPS 50+ PA++++: protetor solar mineral infantil 60 ml</t>
+          <t>1025 Creme Hidratante Dokdo 50ml</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>139.9</v>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Birch Mild-Up Sunscreen UVLock SPF 50 Broad Spectrum</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" s="4" t="n">
-        <v>24.99</v>
-      </c>
+        <v>261.9</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n"/>
       <c r="I51" s="4" t="n"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>https://roundlab.com/products/birch-juice-mild-up-uvlock-sunscreen</t>
-        </is>
-      </c>
-      <c r="L51" s="2">
-        <f>ROUND(H51*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
-        <v/>
-      </c>
-      <c r="M51" s="6">
-        <f>IF(OR(D51="",L51=""),"",D51/L51-1)</f>
-        <v/>
-      </c>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MB003102</t>
+          <t>MB003122</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Óleo de Limpeza Dokdo 1025 200ml</t>
+          <t>For Men Birch Moisturizing Lotion: loção hidratante masculina de bétula 200 ml</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>188.9</v>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1025 Dokdo Toner</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>200ml</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="I52" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>https://roundlab.com/products/1025-dokdo-toner?variant=43023567749334</t>
-        </is>
-      </c>
-      <c r="L52" s="2">
-        <f>ROUND(H52*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
-        <v/>
-      </c>
-      <c r="M52" s="6">
-        <f>IF(OR(D52="",L52=""),"",D52/L52-1)</f>
-        <v/>
-      </c>
+        <v>128.9</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MB003122</t>
+          <t>MB003051</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>For Men Birch Moisturizing Lotion: loção hidratante masculina de bétula 200 ml</t>
+          <t>Shampoo Calmante de Pinheiro e Cica 400ml</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3401,7 +3339,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>128.9</v>
+        <v>159.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3416,21 +3354,21 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MB003051</t>
+          <t>MB003091</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Shampoo Calmante de Pinheiro e Cica 400ml</t>
+          <t>Ampola Calmante de Pinheiro e Cica 30ml</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>159.9</v>
+        <v>181.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3445,12 +3383,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MB003091</t>
+          <t>MB003054</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ampola Calmante de Pinheiro e Cica 30ml</t>
+          <t>Ampola Firmadora de Colágeno Profundo Camélia 30ml</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3459,7 +3397,7 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>181.9</v>
+        <v>233.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3474,12 +3412,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MB003054</t>
+          <t>MB003078</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ampola Firmadora de Colágeno Profundo Camélia 30ml</t>
+          <t>Ampola Hidratante de Bétula 50ml</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3488,7 +3426,7 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>233.9</v>
+        <v>191.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3503,12 +3441,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MB003078</t>
+          <t>MB003040</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ampola Hidratante de Bétula 50ml</t>
+          <t>Ampola calmante de pinheiro e cica 50 ml</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3517,7 +3455,7 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>191.9</v>
+        <v>182.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3532,12 +3470,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MB003040</t>
+          <t>MB003073</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ampola calmante de pinheiro e cica 50 ml</t>
+          <t>Ampola calmante para o couro cabeludo com cica e pinheiro 15 ml</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3546,7 +3484,7 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>182.9</v>
+        <v>123.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3561,12 +3499,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MB003073</t>
+          <t>MB003033</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ampola calmante para o couro cabeludo com cica e pinheiro 15 ml</t>
+          <t>Ampola de Pantenol de Soja Preta 50ml</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3575,7 +3513,7 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>123.9</v>
+        <v>92.64</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3590,12 +3528,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MB003033</t>
+          <t>MB003049</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ampola de Pantenol de Soja Preta 50ml</t>
+          <t>Baby Mild Cream: creme hidratante suave para bebês e crianças 200 ml</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3604,7 +3542,7 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>92.64</v>
+        <v>171.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3619,12 +3557,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MB003049</t>
+          <t>MB003043</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Baby Mild Cream: creme hidratante suave para bebês e crianças 200 ml</t>
+          <t>Baby Mild Top to Toe Wash: sabonete líquido suave da cabeça aos pés 300 ml</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3633,7 +3571,7 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>171.9</v>
+        <v>133.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3648,12 +3586,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MB003043</t>
+          <t>MB003108</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Baby Mild Top to Toe Wash: sabonete líquido suave da cabeça aos pés 300 ml</t>
+          <t>Birch Wax Washing Moisturizer 80ml</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3662,7 +3600,7 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>133.9</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3677,12 +3615,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MB003108</t>
+          <t>MB003076</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Birch Wax Washing Moisturizer 80ml</t>
+          <t>Birch: espuma de barbear masculina 120 ml</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3691,7 +3629,7 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>66.95999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -5175,12 +5113,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId52"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5191,7 +5127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -6776,15 +6712,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Birch Moisturizing Sunscreen UVLock SPF 50 Broad Spectrum [Subscription]</t>
+          <t>Birch Moisturizing Toner</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="D51" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -6794,24 +6727,27 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>RLB119V02-S</t>
+          <t>RLBJT300</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/round-lab-birch-moisturizing-sunscreen-spf-50-pa</t>
+          <t>https://roundlab.com/products/birch-moisturizing-toner</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Birch Moisturizing Toner</t>
+          <t>Birch Moisturizing Toner Pad</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>27</v>
+        <v>23.8</v>
+      </c>
+      <c r="D52" t="n">
+        <v>28</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -6821,27 +6757,27 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>RLBJT300</t>
+          <t>RLBJMP80</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/birch-moisturizing-toner</t>
+          <t>https://roundlab.com/products/birch-moisturizing-pad</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Birch Moisturizing Toner Pad</t>
+          <t>Birch Moisturizing Wash Off Mask</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="D53" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -6851,118 +6787,122 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>RLBJMP80</t>
+          <t>RLBJWOP</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/birch-moisturizing-pad</t>
+          <t>https://roundlab.com/products/birch-moisturizing-wash-off-mask</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Birch Moisturizing Wash Off Mask</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>Birch Sunscreen + Birch Cream Duo</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Birch Moisturizing Cream + Birch Moisturizing Sunscreen UVLock SPF 45+ Broad Spectrum</t>
+        </is>
+      </c>
       <c r="C54" t="n">
-        <v>22.1</v>
+        <v>45.74</v>
       </c>
       <c r="D54" t="n">
-        <v>26</v>
+        <v>60.99</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>RLBJWOP</t>
+          <t>acc74c10-191e-4006-9a3c-974fcd227ae4</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/birch-moisturizing-wash-off-mask</t>
+          <t>https://roundlab.com/products/birch-sunscreen-birch-cream-duo</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Birch Sunscreen + Birch Cream Duo</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Birch Moisturizing Cream + Birch Moisturizing Sunscreen UVLock SPF 45+ Broad Spectrum</t>
-        </is>
-      </c>
+          <t>Birch Sunscreen Mini 10ml</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>45.74</v>
-      </c>
-      <c r="D55" t="n">
-        <v>60.99</v>
+        <v>6.99</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>acc74c10-191e-4006-9a3c-974fcd227ae4</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/birch-sunscreen-birch-cream-duo</t>
+          <t>https://roundlab.com/products/mini-birch-sunscreen</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Birch Sunscreen Mini 10ml</t>
+          <t>Birch Sunscreen Trio</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>6.99</v>
+        <v>60.74</v>
+      </c>
+      <c r="D56" t="n">
+        <v>80.98999999999999</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>36af67f5-7333-40b2-bd65-ffacefba9b25</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/mini-birch-sunscreen</t>
+          <t>https://roundlab.com/products/birch-sunscreen-trio</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Birch Sunscreen Trio</t>
+          <t>Camellia Collagen Anti-Aging Routine Bundle</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>60.74</v>
+        <v>55.5</v>
       </c>
       <c r="D57" t="n">
-        <v>80.98999999999999</v>
+        <v>74</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -6976,27 +6916,31 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>36af67f5-7333-40b2-bd65-ffacefba9b25</t>
+          <t>d545d934-cc0f-4852-bcf2-80f756b247ea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/birch-sunscreen-trio</t>
+          <t>https://roundlab.com/products/collagen-anti-aging-routine-bundle</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Camellia Collagen Anti-Aging Routine Bundle</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>Camellia Collagen Slow Aging Routine</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Camellia Deep Collagen Firming Ampoule + Camellia Deep Collagen Firming Cream + 4 pc Camellia Deep Collagen Firming Gel Mask + Camellia Deep Collagen Jelly Mask Cleanser + 1 PC Camellia Deep Collagen V Lifting Gel Mask</t>
+        </is>
+      </c>
       <c r="C58" t="n">
-        <v>55.5</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>74</v>
+        <v>116.99</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -7010,62 +6954,51 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>d545d934-cc0f-4852-bcf2-80f756b247ea</t>
+          <t>b99ccdb4-2fc8-4a14-947b-24465ac592ae</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/collagen-anti-aging-routine-bundle</t>
+          <t>https://roundlab.com/products/camellia-collagen-slow-aging-routine</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Camellia Collagen Slow Aging Routine</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Camellia Deep Collagen Firming Ampoule + Camellia Deep Collagen Firming Cream + 4 pc Camellia Deep Collagen Firming Gel Mask + Camellia Deep Collagen Jelly Mask Cleanser + 1 PC Camellia Deep Collagen V Lifting Gel Mask</t>
-        </is>
-      </c>
+          <t>Camellia Deep Collagen Eye Cream 30ml</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>87.73999999999999</v>
-      </c>
-      <c r="D59" t="n">
-        <v>116.99</v>
+        <v>30</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>b99ccdb4-2fc8-4a14-947b-24465ac592ae</t>
+          <t>RS14W0002</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-collagen-slow-aging-routine</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-eye-cream-30ml</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Eye Cream 30ml</t>
+          <t>Camellia Deep Collagen Firming Ampoule</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -7075,89 +7008,93 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>RS14W0002</t>
+          <t>RLB109V07</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-eye-cream-30ml</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-firming-ampoule</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Firming Ampoule</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>Camellia Deep Collagen Firming Complete Routine Anti-Aging Bundle</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Camellia Deep Collagen Firming Ampoule + Camellia Deep Collagen Firming Cream + 4 pc Camellia Deep Collagen Firming Gel Mask + Camellia Deep Collagen Jelly Mask Cleanser + 1 PC Camellia Deep Collagen V Lifting Gel Mask + Camellia Deep Collagen Eye Crea...</t>
+        </is>
+      </c>
       <c r="C61" t="n">
-        <v>32</v>
+        <v>140.79</v>
+      </c>
+      <c r="D61" t="n">
+        <v>175.99</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>RLB109V07</t>
+          <t>53a2d331-4137-42e9-ad29-b42085583b08</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-firming-ampoule</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-firming-complete-routine-anti-aging-bundle</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Firming Complete Routine Anti-Aging Bundle</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Camellia Deep Collagen Firming Ampoule + Camellia Deep Collagen Firming Cream + 4 pc Camellia Deep Collagen Firming Gel Mask + Camellia Deep Collagen Jelly Mask Cleanser + 1 PC Camellia Deep Collagen V Lifting Gel Mask + Camellia Deep Collagen Eye Crea...</t>
-        </is>
-      </c>
+          <t>Camellia Deep Collagen Firming Cream</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>140.79</v>
-      </c>
-      <c r="D62" t="n">
-        <v>175.99</v>
+        <v>36</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Esgotado</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>53a2d331-4137-42e9-ad29-b42085583b08</t>
+          <t>RLB104V07</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-firming-complete-routine-anti-aging-bundle</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-firming-cream</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Firming Cream</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>Camellia Deep Collagen Firming Gel Mask</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
       <c r="C63" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -7167,12 +7104,12 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>RLB104V07</t>
+          <t>RLB108V02</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-firming-cream</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-firming-gel-mask?variant=46577419976918</t>
         </is>
       </c>
     </row>
@@ -7184,11 +7121,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1 pc</t>
+          <t>4 pc</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -7198,28 +7135,24 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>RLB108V02</t>
+          <t>RLB108V01</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-firming-gel-mask?variant=46577419976918</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-firming-gel-mask?variant=46577420009686</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Firming Gel Mask</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>4 pc</t>
-        </is>
-      </c>
+          <t>Camellia Deep Collagen Jelly Mask Cleanser</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -7229,24 +7162,24 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>RLB108V01</t>
+          <t>RC14W0001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-firming-gel-mask?variant=46577420009686</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-jelly-mask-cleanser</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Jelly Mask Cleanser</t>
+          <t>Camellia Deep Collagen Lifting Gua Sha Cream</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -7256,24 +7189,24 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>RC14W0001</t>
+          <t>RS14W0003</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-jelly-mask-cleanser</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-lifting-gua-sha-cream</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Lifting Gua Sha Cream</t>
+          <t>Camellia Deep Collagen Milky PDRN Toner 150ml</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -7283,24 +7216,28 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>RS14W0003</t>
+          <t>RS14W0001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-lifting-gua-sha-cream</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-milky-pdrn-toner-150ml</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen Milky PDRN Toner 150ml</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>Camellia Deep Collagen V Lifting Gel Mask</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1 PC</t>
+        </is>
+      </c>
       <c r="C68" t="n">
-        <v>29</v>
+        <v>5.99</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -7310,12 +7247,12 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>RS14W0001</t>
+          <t>RM14W0001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-milky-pdrn-toner-150ml</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-v-lifting-gel-mask?variant=47349673328854</t>
         </is>
       </c>
     </row>
@@ -7327,26 +7264,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1 PC</t>
+          <t>14PC</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5.99</v>
+        <v>42.99</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>RM14W0001</t>
+          <t>RM14W0003</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-v-lifting-gel-mask?variant=47349673328854</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-v-lifting-gel-mask?variant=47056525787350</t>
         </is>
       </c>
     </row>
@@ -7358,80 +7295,83 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14PC</t>
+          <t>4PC</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>42.99</v>
+        <v>20.99</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>RM14W0003</t>
+          <t>RM14W0002</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-v-lifting-gel-mask?variant=47056525787350</t>
+          <t>https://roundlab.com/products/camellia-deep-collagen-v-lifting-gel-mask?variant=47056525820118</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Camellia Deep Collagen V Lifting Gel Mask</t>
+          <t>Daily Hydration Essentials Sheet Mask Bundle (50pcs)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4PC</t>
+          <t>10 PC Soybean Nourishing Sheet Mask + 10 PC 1025 Dokdo Water Gel Mask Sheet + 10 PC Birch Moisturizing Sheet Mask + 10 PC Pine Calming Cica Sheet Mask + 10 pc Birch Moisturizing Double Gel Mask</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>20.99</v>
+        <v>138</v>
+      </c>
+      <c r="D71" t="n">
+        <v>184</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>RM14W0002</t>
+          <t>a20521e0-bf0e-4ae1-b9f0-3d483745fcc7</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/camellia-deep-collagen-v-lifting-gel-mask?variant=47056525820118</t>
+          <t>https://roundlab.com/products/bundle-daily-mask-bundle-bulk</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Daily Hydration Essentials Sheet Mask Bundle (50pcs)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>10 PC Soybean Nourishing Sheet Mask + 10 PC 1025 Dokdo Water Gel Mask Sheet + 10 PC Birch Moisturizing Sheet Mask + 10 PC Pine Calming Cica Sheet Mask + 10 pc Birch Moisturizing Double Gel Mask</t>
-        </is>
-      </c>
+          <t>Dokdo Cleanser Double Bundle</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="D72" t="n">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7441,91 +7381,95 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>a20521e0-bf0e-4ae1-b9f0-3d483745fcc7</t>
+          <t>RL1025DCLBUNDLE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/bundle-daily-mask-bundle-bulk</t>
+          <t>https://roundlab.com/products/dokdo-cleanser-double-1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dokdo Cleanser Double Bundle</t>
+          <t>Dokdo Cleansing Water</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D73" t="n">
         <v>28</v>
       </c>
-      <c r="D73" t="n">
-        <v>34</v>
-      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>RL1025DCLBUNDLE</t>
+          <t>RL1025DCW</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/dokdo-cleanser-double-1</t>
+          <t>https://roundlab.com/products/dokdo-cleansing-water</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dokdo Cleansing Water</t>
+          <t>Dokdo Double Cleansing Bundle</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>22.4</v>
+        <v>39</v>
       </c>
       <c r="D74" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>RL1025DCW</t>
+          <t>DOKDOCLOIL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/dokdo-cleansing-water</t>
+          <t>https://roundlab.com/products/dokdo-cleanser-dokdo-cleansing-oil-bundle-gift</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dokdo Double Cleansing Bundle</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>Dokdo Skin Barrier Hydration Routine Bundle</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>200ml 1025 Dokdo Toner + 1025 Dokdo Lotion + 1025 Dokdo Cream + 1025 Dokdo Cleanser + 1025 Dokdo Ampoule + 1 PC 1025 Dokdo Water Gel Mask Sheet</t>
+        </is>
+      </c>
       <c r="C75" t="n">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="D75" t="n">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -7539,31 +7483,27 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DOKDOCLOIL</t>
+          <t>c15d3c98-f451-479f-b4e3-5693e838a94c</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/dokdo-cleanser-dokdo-cleansing-oil-bundle-gift</t>
+          <t>https://roundlab.com/products/dokdo-skin-barrier-hydration-routine</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Dokdo Skin Barrier Hydration Routine Bundle</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>200ml 1025 Dokdo Toner + 1025 Dokdo Lotion + 1025 Dokdo Cream + 1025 Dokdo Cleanser + 1025 Dokdo Ampoule + 1 PC 1025 Dokdo Water Gel Mask Sheet</t>
-        </is>
-      </c>
+          <t>Hydration &amp; Suncare Essentials Trio</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>107</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>127</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -7577,58 +7517,51 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>c15d3c98-f451-479f-b4e3-5693e838a94c</t>
+          <t>a5342e9f-5815-4272-b3fa-c21143e6c8ef</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/dokdo-skin-barrier-hydration-routine</t>
+          <t>https://roundlab.com/products/suncare-trio</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Hydration &amp; Suncare Essentials Trio</t>
+          <t>Mugwort Calming Cleanser</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>66.29000000000001</v>
-      </c>
-      <c r="D77" t="n">
-        <v>77.98999999999999</v>
+        <v>17</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>a5342e9f-5815-4272-b3fa-c21143e6c8ef</t>
+          <t>RLMCL150</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/suncare-trio</t>
+          <t>https://roundlab.com/products/mugwort-calming-cleanser</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mugwort Calming Cleanser</t>
+          <t>Mugwort Calming Cream</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -7638,85 +7571,89 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>RLMCL150</t>
+          <t>RLMCC300</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/mugwort-calming-cleanser</t>
+          <t>https://roundlab.com/products/mugwort-calming-cream</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mugwort Calming Cream</t>
+          <t>Mugwort Calming Routine Bundle</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>36</v>
+        <v>86.25</v>
+      </c>
+      <c r="D79" t="n">
+        <v>115</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>RLMCC300</t>
+          <t>f52ab8b9-8617-44f1-b8ce-5b233a78069f</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/mugwort-calming-cream</t>
+          <t>https://roundlab.com/products/mugwort-routine-bundle</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mugwort Calming Routine Bundle</t>
+          <t>Mugwort Calming Serum</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>86.25</v>
-      </c>
-      <c r="D80" t="n">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>f52ab8b9-8617-44f1-b8ce-5b233a78069f</t>
+          <t>RLMCS50</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/mugwort-routine-bundle</t>
+          <t>https://roundlab.com/products/mugwort-calming-serum</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mugwort Calming Serum</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>Mugwort Calming Sheet Mask</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1 PC</t>
+        </is>
+      </c>
       <c r="C81" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -7726,12 +7663,12 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>RLMCS50</t>
+          <t>RLMCSM1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/mugwort-calming-serum</t>
+          <t>https://roundlab.com/products/mugwort-calming-sheet-mask?variant=43610238386390</t>
         </is>
       </c>
     </row>
@@ -7743,11 +7680,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1 PC</t>
+          <t>10 PC</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -7757,12 +7694,12 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>RLMCSM1</t>
+          <t>RLMCSM3</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/mugwort-calming-sheet-mask?variant=43610238386390</t>
+          <t>https://roundlab.com/products/mugwort-calming-sheet-mask?variant=43734089793750</t>
         </is>
       </c>
     </row>
@@ -7774,11 +7711,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>10 PC</t>
+          <t>5 PC</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -7788,28 +7725,24 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>RLMCSM3</t>
+          <t>RLMCSM2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/mugwort-calming-sheet-mask?variant=43734089793750</t>
+          <t>https://roundlab.com/products/mugwort-calming-sheet-mask?variant=43610238419158</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mugwort Calming Sheet Mask</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>5 PC</t>
-        </is>
-      </c>
+          <t>Mugwort Calming Toner</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -7819,85 +7752,85 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>RLMCSM2</t>
+          <t>RLMCT300</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/mugwort-calming-sheet-mask?variant=43610238419158</t>
+          <t>https://roundlab.com/products/mugwort-calming-toner</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mugwort Calming Toner</t>
+          <t>Nourishing Soybean Hydration Routine Bundle</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>27</v>
+        <v>98.7</v>
+      </c>
+      <c r="D85" t="n">
+        <v>141</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>RLMCT300</t>
+          <t>935fef0d-9bd2-42f1-8335-24f56d4f4cb9</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/mugwort-calming-toner</t>
+          <t>https://roundlab.com/products/spilling-the-beans-winter-hydration-bundle</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Nourishing Soybean Hydration Routine Bundle</t>
+          <t>Pine Calming Cica Ampoule</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="D86" t="n">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>935fef0d-9bd2-42f1-8335-24f56d4f4cb9</t>
+          <t>RLPCA30</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/spilling-the-beans-winter-hydration-bundle</t>
+          <t>https://roundlab.com/products/pine-tree-cica-care-ampoule</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Ampoule</t>
+          <t>Pine Calming Cica Body Wash</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -7907,81 +7840,81 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>RLPCA30</t>
+          <t>RLPCBDWH</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-tree-cica-care-ampoule</t>
+          <t>https://roundlab.com/products/pine-cica-calming-body-wash</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Body Wash</t>
+          <t>Pine Calming Cica Body and Scalp Care Bundle</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>24</v>
+        <v>61.2</v>
+      </c>
+      <c r="D88" t="n">
+        <v>68</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>RLPCBDWH</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-cica-calming-body-wash</t>
+          <t>https://roundlab.com/products/pine-calming-cica-body-and-scalp-care-bundle-1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Body and Scalp Care Bundle</t>
+          <t>Pine Calming Cica Cleanser</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="D89" t="n">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>RLPCCLSR</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-calming-cica-body-and-scalp-care-bundle-1</t>
+          <t>https://roundlab.com/products/pine-calming-cica-cleanser</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Cleanser</t>
+          <t>Pine Calming Cica Cream</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -7991,24 +7924,24 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>RLPCCLSR</t>
+          <t>RLPCC50</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-calming-cica-cleanser</t>
+          <t>https://roundlab.com/products/pine-tree-cica-cream</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Cream</t>
+          <t>Pine Calming Cica Lotion</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -8018,24 +7951,24 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>RLPCC50</t>
+          <t>RLPCCL</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-tree-cica-cream</t>
+          <t>https://roundlab.com/products/pine-calming-cica-lotion</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Lotion</t>
+          <t>Pine Calming Cica Primer Sunscreen 50ml</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>28</v>
+        <v>24.99</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -8045,24 +7978,24 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>RLPCCL</t>
+          <t>RU03G0002</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-calming-cica-lotion</t>
+          <t>https://roundlab.com/products/pine-calming-cica-primer-sunscreen-50ml</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Primer Sunscreen 50ml</t>
+          <t>Pine Calming Cica Shampoo</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>24.99</v>
+        <v>22</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -8072,24 +8005,28 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>RU03G0002</t>
+          <t>RB03G0004</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-calming-cica-primer-sunscreen-50ml</t>
+          <t>https://roundlab.com/products/pine-calming-cica-shampoo</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Shampoo</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>Pine Calming Cica Sheet Mask</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1 PC</t>
+        </is>
+      </c>
       <c r="C94" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -8099,12 +8036,12 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>RB03G0004</t>
+          <t>RLPCSM27</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-calming-cica-shampoo</t>
+          <t>https://roundlab.com/products/pine-tree-cica-sheet-mask?variant=44067264561366</t>
         </is>
       </c>
     </row>
@@ -8116,11 +8053,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1 PC</t>
+          <t>10 PC</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -8130,12 +8067,12 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>RLPCSM27</t>
+          <t>RLPCSM29</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-tree-cica-sheet-mask?variant=44067264561366</t>
+          <t>https://roundlab.com/products/pine-tree-cica-sheet-mask?variant=43734092054742</t>
         </is>
       </c>
     </row>
@@ -8147,11 +8084,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>10 PC</t>
+          <t>5 PC</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -8161,28 +8098,24 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>RLPCSM29</t>
+          <t>RLPCSM28</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-tree-cica-sheet-mask?variant=43734092054742</t>
+          <t>https://roundlab.com/products/pine-tree-cica-sheet-mask?variant=43610245103830</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Sheet Mask</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>5 PC</t>
-        </is>
-      </c>
+          <t>Pine Calming Cica Toner</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -8192,24 +8125,24 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>RLPCSM28</t>
+          <t>RLPCT250</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-tree-cica-sheet-mask?variant=43610245103830</t>
+          <t>https://roundlab.com/products/pine-calming-cica-toner</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Toner</t>
+          <t>Pine Calming Cica Toner Pad</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -8219,51 +8152,58 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>RLPCT250</t>
+          <t>RLPCP50</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-calming-cica-toner</t>
+          <t>https://roundlab.com/products/pine-tree-cica-pad</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Pine Calming Cica Toner Pad</t>
+          <t>Pine Cica Calming Nose Deep Cleansing Mask Kit (5 pack)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>RLPCP50</t>
+          <t>RM03G0011</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-tree-cica-pad</t>
+          <t>https://roundlab.com/products/pine-cica-calming-nose-deep-cleansing-mask-5-pc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Pine Cica Calming Nose Deep Cleansing Mask Kit (5 pack)</t>
+          <t>Pine Cica Calming Routine Bundle</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>18</v>
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D100" t="n">
+        <v>102</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -8277,58 +8217,51 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>RM03G0011</t>
+          <t>59b520f7-3ee3-4a41-8003-b4260bedb776</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-cica-calming-nose-deep-cleansing-mask-5-pc</t>
+          <t>https://roundlab.com/products/pine-cica-calming-routine</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Pine Cica Calming Routine Bundle</t>
+          <t>Pine Cica Calming Scalp Tonic</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="D101" t="n">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>59b520f7-3ee3-4a41-8003-b4260bedb776</t>
+          <t>RB03W0001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-cica-calming-routine</t>
+          <t>https://roundlab.com/products/pine-cica-calming-scalp-tonic</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Pine Cica Calming Scalp Tonic</t>
+          <t>Pine Cica Deep Pore Clay Mask Cleanser</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -8338,24 +8271,24 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>RB03W0001</t>
+          <t>RC03W0002</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-cica-calming-scalp-tonic</t>
+          <t>https://roundlab.com/products/pine-cica-deep-pore-clay-mask-cleanser</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Pine Cica Deep Pore Clay Mask Cleanser</t>
+          <t>Pine Cica Deep Pore Cleansing Oil 200ml</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -8365,51 +8298,58 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>RC03W0002</t>
+          <t>RC03W0003</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-cica-deep-pore-clay-mask-cleanser</t>
+          <t>https://roundlab.com/products/pine-cica-deep-pore-cleansing-oil-200ml</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Pine Cica Deep Pore Cleansing Oil 200ml</t>
+          <t>Simple Sensitive Skin Routine Bundle</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>RC03W0003</t>
+          <t>BESTCTGRY</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/pine-cica-deep-pore-cleansing-oil-200ml</t>
+          <t>https://roundlab.com/products/dokdo-toner-pine-cica-ampoule-birch-cream-bundle-gift</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Simple Sensitive Skin Routine Bundle</t>
+          <t>Simplest 2 Step Routine- 1025 Dokdo Toner + Birch Moisturizing Cream</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>88</v>
+        <v>50</v>
+      </c>
+      <c r="D105" t="n">
+        <v>53</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -8423,58 +8363,51 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>BESTCTGRY</t>
+          <t>RLDKTBC</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/dokdo-toner-pine-cica-ampoule-birch-cream-bundle-gift</t>
+          <t>https://roundlab.com/products/dokdo-toner-birch-cream-the-perfect-hydration-boost</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Simplest 2 Step Routine- 1025 Dokdo Toner + Birch Moisturizing Cream</t>
+          <t>Soybean Nourishing Cleanser</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>50</v>
-      </c>
-      <c r="D106" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>RLDKTBC</t>
+          <t>RLSNC150</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/dokdo-toner-birch-cream-the-perfect-hydration-boost</t>
+          <t>https://roundlab.com/products/soybean-nourishing-cleanser</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Soybean Nourishing Cleanser</t>
+          <t>Soybean Nourishing Cleansing Oil</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -8484,24 +8417,24 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>RLSNC150</t>
+          <t>RLSCO200</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-nourishing-cleanser</t>
+          <t>https://roundlab.com/products/soybean-nourishing-cleansing-oil</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Soybean Nourishing Cleansing Oil</t>
+          <t>Soybean Nourishing Cream</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -8511,24 +8444,24 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>RLSCO200</t>
+          <t>RLSNC80</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-nourishing-cleansing-oil</t>
+          <t>https://roundlab.com/products/soybean-nourishing-cream</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Soybean Nourishing Cream</t>
+          <t>Soybean Nourishing Serum</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -8538,24 +8471,28 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>RLSNC80</t>
+          <t>RLSNS50</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-nourishing-cream</t>
+          <t>https://roundlab.com/products/soybean-nourishing-serum</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Soybean Nourishing Serum</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
+          <t>Soybean Nourishing Sheet Mask</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1 PC</t>
+        </is>
+      </c>
       <c r="C110" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -8565,12 +8502,12 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>RLSNS50</t>
+          <t>RLSM10</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-nourishing-serum</t>
+          <t>https://roundlab.com/products/soybean-nourishing-sheet-mask?variant=43610248020182</t>
         </is>
       </c>
     </row>
@@ -8582,11 +8519,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1 PC</t>
+          <t>10 PC</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -8596,12 +8533,12 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>RLSM10</t>
+          <t>RLSM12</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-nourishing-sheet-mask?variant=43610248020182</t>
+          <t>https://roundlab.com/products/soybean-nourishing-sheet-mask?variant=43734036414678</t>
         </is>
       </c>
     </row>
@@ -8613,11 +8550,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>10 PC</t>
+          <t>5 PC</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -8627,28 +8564,24 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>RLSM12</t>
+          <t>RLSM11</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-nourishing-sheet-mask?variant=43734036414678</t>
+          <t>https://roundlab.com/products/soybean-nourishing-sheet-mask?variant=43610248052950</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Soybean Nourishing Sheet Mask</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>5 PC</t>
-        </is>
-      </c>
+          <t>Soybean Nourishing Toner</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -8658,85 +8591,85 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>RLSM11</t>
+          <t>RLSNT300</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-nourishing-sheet-mask?variant=43610248052950</t>
+          <t>https://roundlab.com/products/soybean-nourishing-toner</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Soybean Nourishing Toner</t>
+          <t>Soybean Oil Cleanser + Facial Cleanser Double Cleansing Routine</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="D114" t="n">
+        <v>47</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>RLSNT300</t>
+          <t>4ae5f11f-5f12-4c54-8a1d-2216a9bdc60b</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-nourishing-toner</t>
+          <t>https://roundlab.com/products/soybean-double-cleansing-set</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Soybean Oil Cleanser + Facial Cleanser Double Cleansing Routine</t>
+          <t>Soybean Panthenol Ampoule</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>43</v>
-      </c>
-      <c r="D115" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>4ae5f11f-5f12-4c54-8a1d-2216a9bdc60b</t>
+          <t>RLSBPTA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-double-cleansing-set</t>
+          <t>https://roundlab.com/products/soybean-panthenol-ampoule</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Soybean Panthenol Ampoule</t>
+          <t>Soybean Panthenol Cleanser</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -8746,24 +8679,24 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>RLSBPTA</t>
+          <t>RC05G0001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-panthenol-ampoule</t>
+          <t>https://roundlab.com/products/soybean-panthenol-cleanser</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Soybean Panthenol Cleanser</t>
+          <t>Soybean Panthenol Cleansing Oil</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -8773,24 +8706,24 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>RC05G0001</t>
+          <t>RC05G0002</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-panthenol-cleanser</t>
+          <t>https://roundlab.com/products/soybean-panthenol-cleansing-oil</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Soybean Panthenol Cleansing Oil</t>
+          <t>Soybean Panthenol Cream</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -8800,77 +8733,81 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>RC05G0002</t>
+          <t>RLSBPTC</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-panthenol-cleansing-oil</t>
+          <t>https://roundlab.com/products/soybean-panthenol-cream</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Soybean Panthenol Cream</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>Soybean Panthenol Double Cleansing Bundle</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1 PC Soybean Panthenol Mask + Soybean Panthenol Cleanser + Soybean Panthenol Cleansing Oil</t>
+        </is>
+      </c>
       <c r="C119" t="n">
-        <v>38</v>
+        <v>41.39</v>
+      </c>
+      <c r="D119" t="n">
+        <v>45.99</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>RLSBPTC</t>
+          <t>f701bfae-7d07-4fa0-9b40-81aa3c1be2f8</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-panthenol-cream</t>
+          <t>https://roundlab.com/products/soybean-panthenol-double-cleansing-bundle</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Soybean Panthenol Double Cleansing Bundle</t>
+          <t>Soybean Panthenol Sheet Mask</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1 PC Soybean Panthenol Mask + Soybean Panthenol Cleanser + Soybean Panthenol Cleansing Oil</t>
+          <t>1 PC</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>41.39</v>
-      </c>
-      <c r="D120" t="n">
-        <v>45.99</v>
+        <v>3.99</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>f701bfae-7d07-4fa0-9b40-81aa3c1be2f8</t>
+          <t>RLSBPTM-1</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-panthenol-double-cleansing-bundle</t>
+          <t>https://roundlab.com/products/soybean-panthenol-mask?variant=45086692901078</t>
         </is>
       </c>
     </row>
@@ -8882,11 +8819,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1 PC</t>
+          <t>10 PC</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3.99</v>
+        <v>36</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -8896,12 +8833,12 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>RLSBPTM-1</t>
+          <t>RLSBPTM-3</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-panthenol-mask?variant=45086692901078</t>
+          <t>https://roundlab.com/products/soybean-panthenol-mask?variant=45086692966614</t>
         </is>
       </c>
     </row>
@@ -8913,11 +8850,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>10 PC</t>
+          <t>5 PC</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -8927,123 +8864,123 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>RLSBPTM-3</t>
+          <t>RLSBPTM-2</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-panthenol-mask?variant=45086692966614</t>
+          <t>https://roundlab.com/products/soybean-panthenol-mask?variant=45086692933846</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Soybean Panthenol Sheet Mask</t>
+          <t>Soybean Panthenol Skin Barrier Repair Routine</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5 PC</t>
+          <t>Soybean Panthenol Ampoule + Soybean Panthenol Cream + 1 PC Soybean Panthenol Sheet Mask + Soybean Panthenol Cleanser + Soybean Panthenol Cleansing Oil + Soybean Panthenol Toner</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>19</v>
+        <v>107.24</v>
+      </c>
+      <c r="D123" t="n">
+        <v>142.99</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>RLSBPTM-2</t>
+          <t>ea474bee-8c14-4e6b-833d-e1d64a05c45e</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-panthenol-mask?variant=45086692933846</t>
+          <t>https://roundlab.com/products/panthenol-skin-barrier-repair-routine</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Soybean Panthenol Skin Barrier Repair Routine</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Soybean Panthenol Ampoule + Soybean Panthenol Cream + 1 PC Soybean Panthenol Sheet Mask + Soybean Panthenol Cleanser + Soybean Panthenol Cleansing Oil + Soybean Panthenol Toner</t>
-        </is>
-      </c>
+          <t>Soybean Panthenol Toner</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>107.24</v>
-      </c>
-      <c r="D124" t="n">
-        <v>142.99</v>
+        <v>25</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ea474bee-8c14-4e6b-833d-e1d64a05c45e</t>
+          <t>RS05G0007</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/panthenol-skin-barrier-repair-routine</t>
+          <t>https://roundlab.com/products/soybean-panthenol-toner</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Soybean Panthenol Toner</t>
+          <t>Soybean Panthenol Ultimate Hydration &amp; Skin Barrier Repair Duo</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>25</v>
+        <v>71.98999999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>75.98999999999999</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>RS05G0007</t>
+          <t>5e2d8154-3b7c-418c-a5b9-87d102afa867</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-panthenol-toner</t>
+          <t>https://roundlab.com/products/soybean-panthenol-ultimate-hydration-set</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Soybean Panthenol Ultimate Hydration &amp; Skin Barrier Repair Duo</t>
+          <t>Sun Serum Simple Summer Morning Routine</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>71.98999999999999</v>
-      </c>
-      <c r="D126" t="n">
-        <v>75.98999999999999</v>
+        <v>90.39</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -9055,26 +8992,25 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>5e2d8154-3b7c-418c-a5b9-87d102afa867</t>
-        </is>
-      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/soybean-panthenol-ultimate-hydration-set</t>
+          <t>https://roundlab.com/products/sun-serum-simple-summer-morning-routine</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sun Serum Simple Summer Morning Routine</t>
+          <t>Sun-Ready Everywhere Sun Care Bundle</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
-        <v>90.39</v>
+        <v>71.23999999999999</v>
+      </c>
+      <c r="D127" t="n">
+        <v>94.98999999999999</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -9086,56 +9022,53 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>5f6e6adb-a511-49e2-99a0-47cf624c2f67</t>
+        </is>
+      </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/sun-serum-simple-summer-morning-routine</t>
+          <t>https://roundlab.com/products/sun-ready-everywhere-bundle</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sun-Ready Everywhere Sun Care Bundle</t>
+          <t>Vita Niacinamide Dark Spot Cream</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>71.23999999999999</v>
-      </c>
-      <c r="D128" t="n">
-        <v>94.98999999999999</v>
+        <v>33</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>5f6e6adb-a511-49e2-99a0-47cf624c2f67</t>
+          <t>RLB104V08</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/sun-ready-everywhere-bundle</t>
+          <t>https://roundlab.com/products/vita-niacinamide-dark-spot-cream</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Vita Niacinamide Dark Spot Cream</t>
+          <t>Vita Niacinamide Dark Spot Serum</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -9145,24 +9078,28 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>RLB104V08</t>
+          <t>RLB110V08</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/vita-niacinamide-dark-spot-cream</t>
+          <t>https://roundlab.com/products/vita-niacinamide-dark-spot-serum</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Vita Niacinamide Dark Spot Serum</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>Vita Niacinamide Dark Spot Serum Mask</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1 PC</t>
+        </is>
+      </c>
       <c r="C130" t="n">
-        <v>31</v>
+        <v>5.3</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -9172,12 +9109,12 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>RLB110V08</t>
+          <t>RLB108V08</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/vita-niacinamide-dark-spot-serum</t>
+          <t>https://roundlab.com/products/vita-niacinamide-dark-spot-mask?variant=46537314369750</t>
         </is>
       </c>
     </row>
@@ -9189,11 +9126,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1 PC</t>
+          <t>10 PC</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>5.3</v>
+        <v>53.3</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -9203,12 +9140,12 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>RLB108V08</t>
+          <t>RLB108V010</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/vita-niacinamide-dark-spot-mask?variant=46537314369750</t>
+          <t>https://roundlab.com/products/vita-niacinamide-dark-spot-mask?variant=46537314435286</t>
         </is>
       </c>
     </row>
@@ -9220,11 +9157,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>10 PC</t>
+          <t>5 PC</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>53.3</v>
+        <v>26.5</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -9234,119 +9171,122 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>RLB108V010</t>
+          <t>RLB108V09</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/vita-niacinamide-dark-spot-mask?variant=46537314435286</t>
+          <t>https://roundlab.com/products/vita-niacinamide-dark-spot-mask?variant=46537314402518</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Vita Niacinamide Dark Spot Serum Mask</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>5 PC</t>
-        </is>
-      </c>
+          <t>Vita Niacinamide Glass Skin Routine Bundle</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>26.5</v>
+        <v>51.98</v>
+      </c>
+      <c r="D133" t="n">
+        <v>69.3</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>RLB108V09</t>
+          <t>3414535f-2efa-4e90-9da1-e6c8a96a359f</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/vita-niacinamide-dark-spot-mask?variant=46537314402518</t>
+          <t>https://roundlab.com/products/vita-niacinamide-brightening-routine-set</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Vita Niacinamide Glass Skin Routine Bundle</t>
+          <t>Vita Niacinamide Glow Capsule Cream</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>51.98</v>
-      </c>
-      <c r="D134" t="n">
-        <v>69.3</v>
+        <v>28</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>3414535f-2efa-4e90-9da1-e6c8a96a359f</t>
+          <t>RS13W0001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/vita-niacinamide-brightening-routine-set</t>
+          <t>https://roundlab.com/products/vita-niacinamide-glow-capsule-cream</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Vita Niacinamide Glow Capsule Cream</t>
+          <t>[DEAL] Birch Moisturizing Sunscreen Double Bundle</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
-        <v>28</v>
+        <v>39</v>
+      </c>
+      <c r="D135" t="n">
+        <v>56</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Esgotado</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>RS13W0001</t>
+          <t>RLB119V02-2</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/vita-niacinamide-glow-capsule-cream</t>
+          <t>https://roundlab.com/products/double-pack-birch-moisturizing-sunscreen-uvlock-spf-45-broad-spectrum</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>[DEAL] Birch Moisturizing Sunscreen Double Bundle</t>
+          <t>[DEAL] Dokdo Cleanser Double 2-Pack</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D136" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -9358,52 +9298,56 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>RLB119V02-2</t>
-        </is>
-      </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/double-pack-birch-moisturizing-sunscreen-uvlock-spf-45-broad-spectrum</t>
+          <t>https://roundlab.com/products/deal-dokdo-cleanser-double-2-pack</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>[DEAL] Dokdo Cleanser Double 2-Pack</t>
+          <t>[Limited Edition] Birch Moisturizing Lip Balm + Silicone Brush Set</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
-        <v>27</v>
-      </c>
-      <c r="D137" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>RS02W0002</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://roundlab.com/products/deal-dokdo-cleanser-double-2-pack</t>
+          <t>https://roundlab.com/products/birch-moisturizing-lip-balm-brush-set</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>[Limited Edition] Birch Moisturizing Lip Balm + Silicone Brush Set</t>
+          <t>[Limited Edition] Kulani Kinis X Round Lab Sun and After Sun Glow Bundle</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>23</v>
+        <v>110</v>
+      </c>
+      <c r="D138" t="n">
+        <v>141</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -9417,44 +9361,10 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>RS02W0002</t>
+          <t>KULANIKINISBUNDLE</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
-        <is>
-          <t>https://roundlab.com/products/birch-moisturizing-lip-balm-brush-set</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>[Limited Edition] Kulani Kinis X Round Lab Sun and After Sun Glow Bundle</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="n">
-        <v>110</v>
-      </c>
-      <c r="D139" t="n">
-        <v>141</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>KULANIKINISBUNDLE</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
         <is>
           <t>https://roundlab.com/products/limited-edition-kulani-kinis-x-round-lab-sun-and-after-sun-glow-bundle-1</t>
         </is>
@@ -9599,7 +9509,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9647,7 +9556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://roundlab.com · loja "Round Lab" · moeda USD · lido em 30/10/2026 06:02 UTC</t>
+          <t>Site oficial: https://roundlab.com · loja "Round Lab" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
         </is>
       </c>
     </row>
